--- a/GearSage-client/pkgGear/data_raw/evergreen_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/evergreen_rod_import.xlsx
@@ -16171,7 +16171,7 @@
         <v/>
       </c>
       <c r="AC2" t="str" s="1">
-        <v/>
+        <v>War Gazelle RS</v>
       </c>
       <c r="AD2" t="str" s="1">
         <v/>
@@ -16302,7 +16302,7 @@
         <v/>
       </c>
       <c r="AC3" t="str" s="2">
-        <v/>
+        <v>Super Steed GT-R</v>
       </c>
       <c r="AD3" t="str" s="2">
         <v/>
@@ -16433,7 +16433,7 @@
         <v/>
       </c>
       <c r="AC4" t="str" s="1">
-        <v/>
+        <v>Cobra RS</v>
       </c>
       <c r="AD4" t="str" s="1">
         <v/>
@@ -16564,7 +16564,7 @@
         <v/>
       </c>
       <c r="AC5" t="str" s="2">
-        <v/>
+        <v>Cobra GT</v>
       </c>
       <c r="AD5" t="str" s="2">
         <v/>
@@ -16695,7 +16695,7 @@
         <v/>
       </c>
       <c r="AC6" t="str" s="1">
-        <v/>
+        <v>Black Raven Extreme RS</v>
       </c>
       <c r="AD6" t="str" s="1">
         <v/>
@@ -16826,7 +16826,7 @@
         <v/>
       </c>
       <c r="AC7" t="str" s="2">
-        <v/>
+        <v>Stallion RS</v>
       </c>
       <c r="AD7" t="str" s="2">
         <v/>
@@ -16957,7 +16957,7 @@
         <v/>
       </c>
       <c r="AC8" t="str" s="1">
-        <v/>
+        <v>Stallion GT</v>
       </c>
       <c r="AD8" t="str" s="1">
         <v/>
@@ -17088,7 +17088,7 @@
         <v/>
       </c>
       <c r="AC9" t="str" s="2">
-        <v/>
+        <v>Super Raven RS</v>
       </c>
       <c r="AD9" t="str" s="2">
         <v/>
@@ -17219,7 +17219,7 @@
         <v/>
       </c>
       <c r="AC10" t="str" s="1">
-        <v/>
+        <v>Grand Cobra RS</v>
       </c>
       <c r="AD10" t="str" s="1">
         <v/>
@@ -17350,7 +17350,7 @@
         <v/>
       </c>
       <c r="AC11" t="str" s="2">
-        <v/>
+        <v>Grand Cobra GT</v>
       </c>
       <c r="AD11" t="str" s="2">
         <v/>
@@ -17481,7 +17481,7 @@
         <v/>
       </c>
       <c r="AC12" t="str" s="1">
-        <v/>
+        <v>Giant Dire Wolf RS</v>
       </c>
       <c r="AD12" t="str" s="1">
         <v/>
@@ -17612,7 +17612,7 @@
         <v/>
       </c>
       <c r="AC13" t="str" s="2">
-        <v/>
+        <v>Cougar Elite 7 RS</v>
       </c>
       <c r="AD13" t="str" s="2">
         <v/>
@@ -17743,7 +17743,7 @@
         <v/>
       </c>
       <c r="AC14" t="str" s="1">
-        <v/>
+        <v>Cougar Elite 7 GT</v>
       </c>
       <c r="AD14" t="str" s="1">
         <v/>
@@ -17874,7 +17874,7 @@
         <v/>
       </c>
       <c r="AC15" t="str" s="2">
-        <v/>
+        <v>Dire Wolf Wild 7 RS</v>
       </c>
       <c r="AD15" t="str" s="2">
         <v/>
@@ -18005,7 +18005,7 @@
         <v/>
       </c>
       <c r="AC16" t="str" s="1">
-        <v/>
+        <v>Dire Wolf Wild 7 GT-R</v>
       </c>
       <c r="AD16" t="str" s="1">
         <v/>
@@ -18136,7 +18136,7 @@
         <v/>
       </c>
       <c r="AC17" t="str" s="2">
-        <v/>
+        <v>Rapid Gunner RSR</v>
       </c>
       <c r="AD17" t="str" s="2">
         <v/>
@@ -18267,7 +18267,7 @@
         <v/>
       </c>
       <c r="AC18" t="str" s="1">
-        <v/>
+        <v>Rapid Gunner HD</v>
       </c>
       <c r="AD18" t="str" s="1">
         <v/>
@@ -18398,7 +18398,7 @@
         <v/>
       </c>
       <c r="AC19" t="str" s="2">
-        <v/>
+        <v>Super Stallion GT</v>
       </c>
       <c r="AD19" t="str" s="2">
         <v/>
@@ -18529,7 +18529,7 @@
         <v/>
       </c>
       <c r="AC20" t="str" s="1">
-        <v/>
+        <v>Super Stallion GT2RS</v>
       </c>
       <c r="AD20" t="str" s="1">
         <v/>
@@ -18660,7 +18660,7 @@
         <v/>
       </c>
       <c r="AC21" t="str" s="2">
-        <v/>
+        <v>Super Stallion GT3RS</v>
       </c>
       <c r="AD21" t="str" s="2">
         <v/>
@@ -18791,7 +18791,7 @@
         <v/>
       </c>
       <c r="AC22" t="str" s="1">
-        <v/>
+        <v>Grand Stallion GT-X</v>
       </c>
       <c r="AD22" t="str" s="1">
         <v/>
@@ -18922,7 +18922,7 @@
         <v/>
       </c>
       <c r="AC23" t="str" s="2">
-        <v/>
+        <v>Velociraptor RS</v>
       </c>
       <c r="AD23" t="str" s="2">
         <v/>
@@ -19053,7 +19053,7 @@
         <v/>
       </c>
       <c r="AC24" t="str" s="1">
-        <v/>
+        <v>Strider RS</v>
       </c>
       <c r="AD24" t="str" s="1">
         <v/>
@@ -19184,7 +19184,7 @@
         <v/>
       </c>
       <c r="AC25" t="str" s="2">
-        <v/>
+        <v>Stingray Super Shake</v>
       </c>
       <c r="AD25" t="str" s="2">
         <v/>
@@ -19315,7 +19315,7 @@
         <v/>
       </c>
       <c r="AC26" t="str" s="1">
-        <v/>
+        <v>Stingray Super Shake B</v>
       </c>
       <c r="AD26" t="str" s="1">
         <v/>
@@ -19446,7 +19446,7 @@
         <v/>
       </c>
       <c r="AC27" t="str" s="2">
-        <v/>
+        <v>Cobra DG66M</v>
       </c>
       <c r="AD27" t="str" s="2">
         <v/>
@@ -19577,7 +19577,7 @@
         <v/>
       </c>
       <c r="AC28" t="str" s="1">
-        <v/>
+        <v>Cobra DG66M B</v>
       </c>
       <c r="AD28" t="str" s="1">
         <v/>
@@ -19708,7 +19708,7 @@
         <v/>
       </c>
       <c r="AC29" t="str" s="2">
-        <v/>
+        <v>Black Raven</v>
       </c>
       <c r="AD29" t="str" s="2">
         <v/>
@@ -19839,7 +19839,7 @@
         <v/>
       </c>
       <c r="AC30" t="str" s="1">
-        <v/>
+        <v>Black Raven B</v>
       </c>
       <c r="AD30" t="str" s="1">
         <v/>
@@ -19970,7 +19970,7 @@
         <v/>
       </c>
       <c r="AC31" t="str" s="2">
-        <v/>
+        <v>Stallion DG69MH</v>
       </c>
       <c r="AD31" t="str" s="2">
         <v/>
@@ -20101,7 +20101,7 @@
         <v/>
       </c>
       <c r="AC32" t="str" s="1">
-        <v/>
+        <v>Stallion DG69MH B</v>
       </c>
       <c r="AD32" t="str" s="1">
         <v/>
@@ -20232,7 +20232,7 @@
         <v/>
       </c>
       <c r="AC33" t="str" s="2">
-        <v/>
+        <v>Super Cougar</v>
       </c>
       <c r="AD33" t="str" s="2">
         <v/>
@@ -20363,7 +20363,7 @@
         <v/>
       </c>
       <c r="AC34" t="str" s="1">
-        <v/>
+        <v>Super Cougar B</v>
       </c>
       <c r="AD34" t="str" s="1">
         <v/>
@@ -20494,7 +20494,7 @@
         <v/>
       </c>
       <c r="AC35" t="str" s="2">
-        <v/>
+        <v>Gunslinger</v>
       </c>
       <c r="AD35" t="str" s="2">
         <v/>
@@ -20625,7 +20625,7 @@
         <v/>
       </c>
       <c r="AC36" t="str" s="1">
-        <v/>
+        <v>Gunslinger B</v>
       </c>
       <c r="AD36" t="str" s="1">
         <v/>
@@ -20756,7 +20756,7 @@
         <v/>
       </c>
       <c r="AC37" t="str" s="2">
-        <v/>
+        <v>Grand Cobra Limited</v>
       </c>
       <c r="AD37" t="str" s="2">
         <v/>
@@ -20887,7 +20887,7 @@
         <v/>
       </c>
       <c r="AC38" t="str" s="1">
-        <v/>
+        <v>Egoist</v>
       </c>
       <c r="AD38" t="str" s="1">
         <v/>
@@ -21018,7 +21018,7 @@
         <v/>
       </c>
       <c r="AC39" t="str" s="2">
-        <v/>
+        <v>Egoist B</v>
       </c>
       <c r="AD39" t="str" s="2">
         <v/>
@@ -21149,7 +21149,7 @@
         <v/>
       </c>
       <c r="AC40" t="str" s="1">
-        <v/>
+        <v>Super Stallion</v>
       </c>
       <c r="AD40" t="str" s="1">
         <v/>
@@ -21280,7 +21280,7 @@
         <v/>
       </c>
       <c r="AC41" t="str" s="2">
-        <v/>
+        <v>Super Stallion B</v>
       </c>
       <c r="AD41" t="str" s="2">
         <v/>
@@ -21411,7 +21411,7 @@
         <v/>
       </c>
       <c r="AC42" t="str" s="1">
-        <v/>
+        <v>Black Briar</v>
       </c>
       <c r="AD42" t="str" s="1">
         <v/>
@@ -21542,7 +21542,7 @@
         <v/>
       </c>
       <c r="AC43" t="str" s="2">
-        <v/>
+        <v>Black Briar B</v>
       </c>
       <c r="AD43" t="str" s="2">
         <v/>
@@ -21673,7 +21673,7 @@
         <v/>
       </c>
       <c r="AC44" t="str" s="1">
-        <v/>
+        <v>Stingray Wild Finesse</v>
       </c>
       <c r="AD44" t="str" s="1">
         <v/>
@@ -21804,7 +21804,7 @@
         <v/>
       </c>
       <c r="AC45" t="str" s="2">
-        <v/>
+        <v>Stingray Wild Finesse B</v>
       </c>
       <c r="AD45" t="str" s="2">
         <v/>
@@ -21935,7 +21935,7 @@
         <v/>
       </c>
       <c r="AC46" t="str" s="1">
-        <v/>
+        <v>Black Raven SS</v>
       </c>
       <c r="AD46" t="str" s="1">
         <v/>
@@ -22066,7 +22066,7 @@
         <v/>
       </c>
       <c r="AC47" t="str" s="2">
-        <v/>
+        <v>Black Raven SS B</v>
       </c>
       <c r="AD47" t="str" s="2">
         <v/>
@@ -22197,7 +22197,7 @@
         <v/>
       </c>
       <c r="AC48" t="str" s="1">
-        <v/>
+        <v>Incredible Sensor Delges UL</v>
       </c>
       <c r="AD48" t="str" s="1">
         <v/>
@@ -22328,7 +22328,7 @@
         <v/>
       </c>
       <c r="AC49" t="str" s="2">
-        <v/>
+        <v>Incredible Sensor Delges</v>
       </c>
       <c r="AD49" t="str" s="2">
         <v/>
@@ -22459,7 +22459,7 @@
         <v/>
       </c>
       <c r="AC50" t="str" s="1">
-        <v/>
+        <v>Beastinger</v>
       </c>
       <c r="AD50" t="str" s="1">
         <v/>
@@ -22590,7 +22590,7 @@
         <v/>
       </c>
       <c r="AC51" t="str" s="2">
-        <v/>
+        <v>Beastinger Extreme</v>
       </c>
       <c r="AD51" t="str" s="2">
         <v/>
@@ -22721,7 +22721,7 @@
         <v/>
       </c>
       <c r="AC52" t="str" s="1">
-        <v/>
+        <v>Incredible Sensor Galnerius</v>
       </c>
       <c r="AD52" t="str" s="1">
         <v/>
@@ -22852,7 +22852,7 @@
         <v/>
       </c>
       <c r="AC53" t="str" s="2">
-        <v/>
+        <v>Spider Spin</v>
       </c>
       <c r="AD53" t="str" s="2">
         <v/>
@@ -22983,7 +22983,7 @@
         <v/>
       </c>
       <c r="AC54" t="str" s="1">
-        <v/>
+        <v>LL Carolina Special</v>
       </c>
       <c r="AD54" t="str" s="1">
         <v/>
@@ -23114,7 +23114,7 @@
         <v/>
       </c>
       <c r="AC55" t="str" s="2">
-        <v/>
+        <v>Super Finesse</v>
       </c>
       <c r="AD55" t="str" s="2">
         <v/>
@@ -23245,7 +23245,7 @@
         <v/>
       </c>
       <c r="AC56" t="str" s="1">
-        <v/>
+        <v>Sight Eagle</v>
       </c>
       <c r="AD56" t="str" s="1">
         <v/>
@@ -23376,7 +23376,7 @@
         <v/>
       </c>
       <c r="AC57" t="str" s="2">
-        <v/>
+        <v>Mighty Finesse</v>
       </c>
       <c r="AD57" t="str" s="2">
         <v/>
@@ -23507,7 +23507,7 @@
         <v/>
       </c>
       <c r="AC58" t="str" s="1">
-        <v/>
+        <v>Marshall Eagle</v>
       </c>
       <c r="AD58" t="str" s="1">
         <v/>
@@ -23638,7 +23638,7 @@
         <v/>
       </c>
       <c r="AC59" t="str" s="2">
-        <v/>
+        <v>Sight Hawk</v>
       </c>
       <c r="AD59" t="str" s="2">
         <v/>
@@ -23769,7 +23769,7 @@
         <v/>
       </c>
       <c r="AC60" t="str" s="1">
-        <v/>
+        <v>Spin Serpent</v>
       </c>
       <c r="AD60" t="str" s="1">
         <v/>
@@ -23900,7 +23900,7 @@
         <v/>
       </c>
       <c r="AC61" t="str" s="2">
-        <v/>
+        <v>Bush Serpent</v>
       </c>
       <c r="AD61" t="str" s="2">
         <v/>
@@ -24031,7 +24031,7 @@
         <v/>
       </c>
       <c r="AC62" t="str" s="1">
-        <v/>
+        <v>King Serpent</v>
       </c>
       <c r="AD62" t="str" s="1">
         <v/>
@@ -24162,7 +24162,7 @@
         <v/>
       </c>
       <c r="AC63" t="str" s="2">
-        <v/>
+        <v>Alouette</v>
       </c>
       <c r="AD63" t="str" s="2">
         <v/>
@@ -24293,7 +24293,7 @@
         <v/>
       </c>
       <c r="AC64" t="str" s="1">
-        <v/>
+        <v>Degel</v>
       </c>
       <c r="AD64" t="str" s="1">
         <v/>
@@ -24424,7 +24424,7 @@
         <v/>
       </c>
       <c r="AC65" t="str" s="2">
-        <v/>
+        <v>Lightning Strike</v>
       </c>
       <c r="AD65" t="str" s="2">
         <v/>
@@ -24555,7 +24555,7 @@
         <v/>
       </c>
       <c r="AC66" t="str" s="1">
-        <v/>
+        <v>Cantata</v>
       </c>
       <c r="AD66" t="str" s="1">
         <v/>
@@ -24686,7 +24686,7 @@
         <v/>
       </c>
       <c r="AC67" t="str" s="2">
-        <v/>
+        <v>Yumihari</v>
       </c>
       <c r="AD67" t="str" s="2">
         <v/>
@@ -24817,7 +24817,7 @@
         <v/>
       </c>
       <c r="AC68" t="str" s="1">
-        <v/>
+        <v>Fire Sword</v>
       </c>
       <c r="AD68" t="str" s="1">
         <v/>
@@ -24948,7 +24948,7 @@
         <v/>
       </c>
       <c r="AC69" t="str" s="2">
-        <v/>
+        <v>Sky Sword</v>
       </c>
       <c r="AD69" t="str" s="2">
         <v/>
@@ -25079,7 +25079,7 @@
         <v/>
       </c>
       <c r="AC70" t="str" s="1">
-        <v/>
+        <v>Moongazer</v>
       </c>
       <c r="AD70" t="str" s="1">
         <v/>
@@ -25210,7 +25210,7 @@
         <v/>
       </c>
       <c r="AC71" t="str" s="2">
-        <v/>
+        <v>Stargazer</v>
       </c>
       <c r="AD71" t="str" s="2">
         <v/>
@@ -25341,7 +25341,7 @@
         <v/>
       </c>
       <c r="AC72" t="str" s="1">
-        <v/>
+        <v>Black Rose</v>
       </c>
       <c r="AD72" t="str" s="1">
         <v/>
@@ -25472,7 +25472,7 @@
         <v/>
       </c>
       <c r="AC73" t="str" s="2">
-        <v/>
+        <v>Silva</v>
       </c>
       <c r="AD73" t="str" s="2">
         <v/>
@@ -25603,7 +25603,7 @@
         <v/>
       </c>
       <c r="AC74" t="str" s="1">
-        <v/>
+        <v>Throne</v>
       </c>
       <c r="AD74" t="str" s="1">
         <v/>
@@ -25734,7 +25734,7 @@
         <v/>
       </c>
       <c r="AC75" t="str" s="2">
-        <v/>
+        <v>Willow</v>
       </c>
       <c r="AD75" t="str" s="2">
         <v/>
@@ -25865,7 +25865,7 @@
         <v/>
       </c>
       <c r="AC76" t="str" s="1">
-        <v/>
+        <v>Black Guardian</v>
       </c>
       <c r="AD76" t="str" s="1">
         <v/>
@@ -25996,7 +25996,7 @@
         <v/>
       </c>
       <c r="AC77" t="str" s="2">
-        <v/>
+        <v>Hide and Seek</v>
       </c>
       <c r="AD77" t="str" s="2">
         <v/>
@@ -26127,7 +26127,7 @@
         <v/>
       </c>
       <c r="AC78" t="str" s="1">
-        <v/>
+        <v>Quick Senses</v>
       </c>
       <c r="AD78" t="str" s="1">
         <v/>
@@ -26258,7 +26258,7 @@
         <v/>
       </c>
       <c r="AC79" t="str" s="2">
-        <v/>
+        <v>Garza</v>
       </c>
       <c r="AD79" t="str" s="2">
         <v/>
@@ -26389,7 +26389,7 @@
         <v/>
       </c>
       <c r="AC80" t="str" s="1">
-        <v/>
+        <v>Free Will</v>
       </c>
       <c r="AD80" t="str" s="1">
         <v/>
@@ -26520,7 +26520,7 @@
         <v/>
       </c>
       <c r="AC81" t="str" s="2">
-        <v/>
+        <v>EG Action</v>
       </c>
       <c r="AD81" t="str" s="2">
         <v/>
@@ -26651,7 +26651,7 @@
         <v/>
       </c>
       <c r="AC82" t="str" s="1">
-        <v/>
+        <v>Technical Action</v>
       </c>
       <c r="AD82" t="str" s="1">
         <v/>
@@ -26782,7 +26782,7 @@
         <v/>
       </c>
       <c r="AC83" t="str" s="2">
-        <v/>
+        <v>Wallacea</v>
       </c>
       <c r="AD83" t="str" s="2">
         <v/>
@@ -26913,7 +26913,7 @@
         <v/>
       </c>
       <c r="AC84" t="str" s="1">
-        <v/>
+        <v>Manipulator</v>
       </c>
       <c r="AD84" t="str" s="1">
         <v/>
@@ -27044,7 +27044,7 @@
         <v/>
       </c>
       <c r="AC85" t="str" s="2">
-        <v/>
+        <v>Metal Whip</v>
       </c>
       <c r="AD85" t="str" s="2">
         <v/>
@@ -27175,7 +27175,7 @@
         <v/>
       </c>
       <c r="AC86" t="str" s="1">
-        <v/>
+        <v>Air Regius LTS</v>
       </c>
       <c r="AD86" t="str" s="1">
         <v/>
@@ -27306,7 +27306,7 @@
         <v/>
       </c>
       <c r="AC87" t="str" s="2">
-        <v/>
+        <v>Air Regius</v>
       </c>
       <c r="AD87" t="str" s="2">
         <v/>
@@ -27437,7 +27437,7 @@
         <v/>
       </c>
       <c r="AC88" t="str" s="1">
-        <v/>
+        <v>Force Grandis LTS</v>
       </c>
       <c r="AD88" t="str" s="1">
         <v/>
@@ -27568,7 +27568,7 @@
         <v/>
       </c>
       <c r="AC89" t="str" s="2">
-        <v/>
+        <v>Force Grandis</v>
       </c>
       <c r="AD89" t="str" s="2">
         <v/>
@@ -27699,7 +27699,7 @@
         <v/>
       </c>
       <c r="AC90" t="str" s="1">
-        <v/>
+        <v>EG Moving</v>
       </c>
       <c r="AD90" t="str" s="1">
         <v/>
@@ -27830,7 +27830,7 @@
         <v/>
       </c>
       <c r="AC91" t="str" s="2">
-        <v/>
+        <v>Red Meister</v>
       </c>
       <c r="AD91" t="str" s="2">
         <v/>
@@ -27961,7 +27961,7 @@
         <v/>
       </c>
       <c r="AC92" t="str" s="1">
-        <v/>
+        <v>Bluemeister LTS</v>
       </c>
       <c r="AD92" t="str" s="1">
         <v/>
@@ -28092,7 +28092,7 @@
         <v/>
       </c>
       <c r="AC93" t="str" s="2">
-        <v/>
+        <v>Bluemeister</v>
       </c>
       <c r="AD93" t="str" s="2">
         <v/>
@@ -28223,7 +28223,7 @@
         <v/>
       </c>
       <c r="AC94" t="str" s="1">
-        <v/>
+        <v>Pro Guidance C68</v>
       </c>
       <c r="AD94" t="str" s="1">
         <v/>
@@ -28354,7 +28354,7 @@
         <v/>
       </c>
       <c r="AC95" t="str" s="2">
-        <v/>
+        <v>Heracles LTS</v>
       </c>
       <c r="AD95" t="str" s="2">
         <v/>
@@ -28485,7 +28485,7 @@
         <v/>
       </c>
       <c r="AC96" t="str" s="1">
-        <v/>
+        <v>Heracles</v>
       </c>
       <c r="AD96" t="str" s="1">
         <v/>
@@ -28616,7 +28616,7 @@
         <v/>
       </c>
       <c r="AC97" t="str" s="2">
-        <v/>
+        <v>Air Regius 7</v>
       </c>
       <c r="AD97" t="str" s="2">
         <v/>
@@ -28747,7 +28747,7 @@
         <v/>
       </c>
       <c r="AC98" t="str" s="1">
-        <v/>
+        <v>Force Grandis 7</v>
       </c>
       <c r="AD98" t="str" s="1">
         <v/>
@@ -28878,7 +28878,7 @@
         <v/>
       </c>
       <c r="AC99" t="str" s="2">
-        <v/>
+        <v>Force Grandis 7 LTS</v>
       </c>
       <c r="AD99" t="str" s="2">
         <v/>
@@ -29009,7 +29009,7 @@
         <v/>
       </c>
       <c r="AC100" t="str" s="1">
-        <v/>
+        <v>Bluemeister 7</v>
       </c>
       <c r="AD100" t="str" s="1">
         <v/>
@@ -29140,7 +29140,7 @@
         <v/>
       </c>
       <c r="AC101" t="str" s="2">
-        <v/>
+        <v>Bluemeister 7 LTS</v>
       </c>
       <c r="AD101" t="str" s="2">
         <v/>
@@ -29271,7 +29271,7 @@
         <v/>
       </c>
       <c r="AC102" t="str" s="1">
-        <v/>
+        <v>Heracles 7</v>
       </c>
       <c r="AD102" t="str" s="1">
         <v/>
@@ -29402,7 +29402,7 @@
         <v/>
       </c>
       <c r="AC103" t="str" s="2">
-        <v/>
+        <v>Heracles 7 LTS</v>
       </c>
       <c r="AD103" t="str" s="2">
         <v/>
@@ -29533,7 +29533,7 @@
         <v/>
       </c>
       <c r="AC104" t="str" s="1">
-        <v/>
+        <v>EG Swimming</v>
       </c>
       <c r="AD104" t="str" s="1">
         <v/>
@@ -29664,7 +29664,7 @@
         <v/>
       </c>
       <c r="AC105" t="str" s="2">
-        <v/>
+        <v>Super Explosion</v>
       </c>
       <c r="AD105" t="str" s="2">
         <v/>
@@ -29795,7 +29795,7 @@
         <v/>
       </c>
       <c r="AC106" t="str" s="1">
-        <v/>
+        <v>Actaeon</v>
       </c>
       <c r="AD106" t="str" s="1">
         <v/>
@@ -29926,7 +29926,7 @@
         <v/>
       </c>
       <c r="AC107" t="str" s="2">
-        <v/>
+        <v>Airy Flip</v>
       </c>
       <c r="AD107" t="str" s="2">
         <v/>
@@ -30057,7 +30057,7 @@
         <v/>
       </c>
       <c r="AC108" t="str" s="1">
-        <v/>
+        <v>Strike Master 77</v>
       </c>
       <c r="AD108" t="str" s="1">
         <v/>
@@ -30188,7 +30188,7 @@
         <v/>
       </c>
       <c r="AC109" t="str" s="2">
-        <v/>
+        <v>Actaeon Magnum EX</v>
       </c>
       <c r="AD109" t="str" s="2">
         <v/>
@@ -30319,7 +30319,7 @@
         <v/>
       </c>
       <c r="AC110" t="str" s="1">
-        <v/>
+        <v>Actaeon Magnum</v>
       </c>
       <c r="AD110" t="str" s="1">
         <v/>
@@ -30450,7 +30450,7 @@
         <v/>
       </c>
       <c r="AC111" t="str" s="2">
-        <v/>
+        <v>Sparkshot</v>
       </c>
       <c r="AD111" t="str" s="2">
         <v/>
@@ -30581,7 +30581,7 @@
         <v/>
       </c>
       <c r="AC112" t="str" s="1">
-        <v/>
+        <v>Torquata 66</v>
       </c>
       <c r="AD112" t="str" s="1">
         <v/>
@@ -30712,7 +30712,7 @@
         <v/>
       </c>
       <c r="AC113" t="str" s="2">
-        <v/>
+        <v>Ocelot</v>
       </c>
       <c r="AD113" t="str" s="2">
         <v/>
@@ -30843,7 +30843,7 @@
         <v/>
       </c>
       <c r="AC114" t="str" s="1">
-        <v/>
+        <v>Serval</v>
       </c>
       <c r="AD114" t="str" s="1">
         <v/>
@@ -30974,7 +30974,7 @@
         <v/>
       </c>
       <c r="AC115" t="str" s="2">
-        <v/>
+        <v>Torquata 7</v>
       </c>
       <c r="AD115" t="str" s="2">
         <v/>
@@ -31105,7 +31105,7 @@
         <v/>
       </c>
       <c r="AC116" t="str" s="1">
-        <v/>
+        <v>Leopard</v>
       </c>
       <c r="AD116" t="str" s="1">
         <v/>
@@ -31236,7 +31236,7 @@
         <v/>
       </c>
       <c r="AC117" t="str" s="2">
-        <v/>
+        <v>Black Regius</v>
       </c>
       <c r="AD117" t="str" s="2">
         <v/>
@@ -31367,7 +31367,7 @@
         <v/>
       </c>
       <c r="AC118" t="str" s="1">
-        <v/>
+        <v>UT Spin</v>
       </c>
       <c r="AD118" t="str" s="1">
         <v/>
@@ -31498,7 +31498,7 @@
         <v/>
       </c>
       <c r="AC119" t="str" s="2">
-        <v/>
+        <v>Power Shaker 68ML</v>
       </c>
       <c r="AD119" t="str" s="2">
         <v/>
@@ -31629,7 +31629,7 @@
         <v/>
       </c>
       <c r="AC120" t="str" s="1">
-        <v/>
+        <v>Power Shaker 611M</v>
       </c>
       <c r="AD120" t="str" s="1">
         <v/>
@@ -31760,7 +31760,7 @@
         <v/>
       </c>
       <c r="AC121" t="str" s="2">
-        <v/>
+        <v>Phalanx</v>
       </c>
       <c r="AD121" t="str" s="2">
         <v/>
@@ -31891,7 +31891,7 @@
         <v/>
       </c>
       <c r="AC122" t="str" s="1">
-        <v/>
+        <v>Solid Sensor 61</v>
       </c>
       <c r="AD122" t="str" s="1">
         <v/>
@@ -32022,7 +32022,7 @@
         <v/>
       </c>
       <c r="AC123" t="str" s="2">
-        <v/>
+        <v>HFAC-65M</v>
       </c>
       <c r="AD123" t="str" s="2">
         <v/>
@@ -32153,7 +32153,7 @@
         <v/>
       </c>
       <c r="AC124" t="str" s="1">
-        <v/>
+        <v>HFAC-66ML</v>
       </c>
       <c r="AD124" t="str" s="1">
         <v/>
@@ -32284,7 +32284,7 @@
         <v/>
       </c>
       <c r="AC125" t="str" s="2">
-        <v/>
+        <v>HFAC-511MHST</v>
       </c>
       <c r="AD125" t="str" s="2">
         <v/>
@@ -32415,7 +32415,7 @@
         <v/>
       </c>
       <c r="AC126" t="str" s="1">
-        <v/>
+        <v>HFAC-66MST</v>
       </c>
       <c r="AD126" t="str" s="1">
         <v/>
@@ -32546,7 +32546,7 @@
         <v/>
       </c>
       <c r="AC127" t="str" s="2">
-        <v/>
+        <v>HFAC-67MHST</v>
       </c>
       <c r="AD127" t="str" s="2">
         <v/>
@@ -32677,7 +32677,7 @@
         <v/>
       </c>
       <c r="AC128" t="str" s="1">
-        <v/>
+        <v>HFAC-70HST</v>
       </c>
       <c r="AD128" t="str" s="1">
         <v/>
@@ -32808,7 +32808,7 @@
         <v/>
       </c>
       <c r="AC129" t="str" s="2">
-        <v/>
+        <v>HFAS-511MHST</v>
       </c>
       <c r="AD129" t="str" s="2">
         <v/>
@@ -32939,7 +32939,7 @@
         <v/>
       </c>
       <c r="AC130" t="str" s="1">
-        <v/>
+        <v>HFAS-61ULST</v>
       </c>
       <c r="AD130" t="str" s="1">
         <v/>
@@ -33070,7 +33070,7 @@
         <v/>
       </c>
       <c r="AC131" t="str" s="2">
-        <v/>
+        <v>HFAS-64XULST</v>
       </c>
       <c r="AD131" t="str" s="2">
         <v/>
@@ -33201,7 +33201,7 @@
         <v/>
       </c>
       <c r="AC132" t="str" s="1">
-        <v/>
+        <v>HFAS-65ULST</v>
       </c>
       <c r="AD132" t="str" s="1">
         <v/>
@@ -33332,7 +33332,7 @@
         <v/>
       </c>
       <c r="AC133" t="str" s="2">
-        <v/>
+        <v>Rippin Feat</v>
       </c>
       <c r="AD133" t="str" s="2">
         <v/>
@@ -33463,7 +33463,7 @@
         <v/>
       </c>
       <c r="AC134" t="str" s="1">
-        <v/>
+        <v>Multi Roller</v>
       </c>
       <c r="AD134" t="str" s="1">
         <v/>
@@ -33594,7 +33594,7 @@
         <v/>
       </c>
       <c r="AC135" t="str" s="2">
-        <v/>
+        <v>Super Detonator</v>
       </c>
       <c r="AD135" t="str" s="2">
         <v/>
@@ -33725,7 +33725,7 @@
         <v/>
       </c>
       <c r="AC136" t="str" s="1">
-        <v/>
+        <v>Super Triumph</v>
       </c>
       <c r="AD136" t="str" s="1">
         <v/>
@@ -33856,7 +33856,7 @@
         <v/>
       </c>
       <c r="AC137" t="str" s="2">
-        <v/>
+        <v>Super Magnum</v>
       </c>
       <c r="AD137" t="str" s="2">
         <v/>
@@ -33987,7 +33987,7 @@
         <v/>
       </c>
       <c r="AC138" t="str" s="1">
-        <v/>
+        <v>Razor Shot</v>
       </c>
       <c r="AD138" t="str" s="1">
         <v/>
@@ -34118,7 +34118,7 @@
         <v/>
       </c>
       <c r="AC139" t="str" s="2">
-        <v/>
+        <v>Fieldin Star Bait Finesse</v>
       </c>
       <c r="AD139" t="str" s="2">
         <v/>
@@ -34249,7 +34249,7 @@
         <v/>
       </c>
       <c r="AC140" t="str" s="1">
-        <v/>
+        <v>Shooting Star</v>
       </c>
       <c r="AD140" t="str" s="1">
         <v/>
@@ -34380,7 +34380,7 @@
         <v/>
       </c>
       <c r="AC141" t="str" s="2">
-        <v/>
+        <v>Warrior</v>
       </c>
       <c r="AD141" t="str" s="2">
         <v/>
@@ -34511,7 +34511,7 @@
         <v/>
       </c>
       <c r="AC142" t="str" s="1">
-        <v/>
+        <v>Tempest</v>
       </c>
       <c r="AD142" t="str" s="1">
         <v/>
@@ -34642,7 +34642,7 @@
         <v/>
       </c>
       <c r="AC143" t="str" s="2">
-        <v/>
+        <v>Tyrant</v>
       </c>
       <c r="AD143" t="str" s="2">
         <v/>
@@ -34773,7 +34773,7 @@
         <v/>
       </c>
       <c r="AC144" t="str" s="1">
-        <v/>
+        <v>Wild Shooter</v>
       </c>
       <c r="AD144" t="str" s="1">
         <v/>
@@ -34904,7 +34904,7 @@
         <v/>
       </c>
       <c r="AC145" t="str" s="2">
-        <v/>
+        <v>Sharp Shooter</v>
       </c>
       <c r="AD145" t="str" s="2">
         <v/>
@@ -35035,7 +35035,7 @@
         <v/>
       </c>
       <c r="AC146" t="str" s="1">
-        <v/>
+        <v>Explorer</v>
       </c>
       <c r="AD146" t="str" s="1">
         <v/>
@@ -35166,7 +35166,7 @@
         <v/>
       </c>
       <c r="AC147" t="str" s="2">
-        <v/>
+        <v>Power Plant</v>
       </c>
       <c r="AD147" t="str" s="2">
         <v/>
@@ -35297,7 +35297,7 @@
         <v/>
       </c>
       <c r="AC148" t="str" s="1">
-        <v/>
+        <v>Digger</v>
       </c>
       <c r="AD148" t="str" s="1">
         <v/>
@@ -35428,7 +35428,7 @@
         <v/>
       </c>
       <c r="AC149" t="str" s="2">
-        <v/>
+        <v>Black Actaeon</v>
       </c>
       <c r="AD149" t="str" s="2">
         <v/>
@@ -35559,7 +35559,7 @@
         <v/>
       </c>
       <c r="AC150" t="str" s="1">
-        <v/>
+        <v>Master Archer 56</v>
       </c>
       <c r="AD150" t="str" s="1">
         <v/>
@@ -35690,7 +35690,7 @@
         <v/>
       </c>
       <c r="AC151" t="str" s="2">
-        <v/>
+        <v>Drift Master</v>
       </c>
       <c r="AD151" t="str" s="2">
         <v/>
@@ -35821,7 +35821,7 @@
         <v/>
       </c>
       <c r="AC152" t="str" s="1">
-        <v/>
+        <v>Spitfire</v>
       </c>
       <c r="AD152" t="str" s="1">
         <v/>
@@ -35952,7 +35952,7 @@
         <v/>
       </c>
       <c r="AC153" t="str" s="2">
-        <v/>
+        <v>Smooth Torque</v>
       </c>
       <c r="AD153" t="str" s="2">
         <v/>
@@ -36083,7 +36083,7 @@
         <v/>
       </c>
       <c r="AC154" t="str" s="1">
-        <v/>
+        <v>Fortune Blue</v>
       </c>
       <c r="AD154" t="str" s="1">
         <v/>
@@ -36214,7 +36214,7 @@
         <v/>
       </c>
       <c r="AC155" t="str" s="2">
-        <v/>
+        <v>CLCC-68ML</v>
       </c>
       <c r="AD155" t="str" s="2">
         <v/>
@@ -36345,7 +36345,7 @@
         <v/>
       </c>
       <c r="AC156" t="str" s="1">
-        <v/>
+        <v>CLCC-610M</v>
       </c>
       <c r="AD156" t="str" s="1">
         <v/>
@@ -36476,7 +36476,7 @@
         <v/>
       </c>
       <c r="AC157" t="str" s="2">
-        <v/>
+        <v>CLCC-611MH</v>
       </c>
       <c r="AD157" t="str" s="2">
         <v/>
@@ -36607,7 +36607,7 @@
         <v/>
       </c>
       <c r="AC158" t="str" s="1">
-        <v/>
+        <v>CLCC-71MH</v>
       </c>
       <c r="AD158" t="str" s="1">
         <v/>
@@ -36738,7 +36738,7 @@
         <v/>
       </c>
       <c r="AC159" t="str" s="2">
-        <v/>
+        <v>CLCC-71H</v>
       </c>
       <c r="AD159" t="str" s="2">
         <v/>
@@ -36869,7 +36869,7 @@
         <v/>
       </c>
       <c r="AC160" t="str" s="1">
-        <v/>
+        <v>CLCS-611L</v>
       </c>
       <c r="AD160" t="str" s="1">
         <v/>
@@ -37000,7 +37000,7 @@
         <v/>
       </c>
       <c r="AC161" t="str" s="2">
-        <v/>
+        <v>CLCS-70ML</v>
       </c>
       <c r="AD161" t="str" s="2">
         <v/>
@@ -37131,7 +37131,7 @@
         <v/>
       </c>
       <c r="AC162" t="str" s="1">
-        <v/>
+        <v>CLCS-75M</v>
       </c>
       <c r="AD162" t="str" s="1">
         <v/>
@@ -37262,7 +37262,7 @@
         <v/>
       </c>
       <c r="AC163" t="str" s="2">
-        <v/>
+        <v>CLCS-77MH</v>
       </c>
       <c r="AD163" t="str" s="2">
         <v/>
@@ -37393,7 +37393,7 @@
         <v/>
       </c>
       <c r="AC164" t="str" s="1">
-        <v/>
+        <v>Aerial</v>
       </c>
       <c r="AD164" t="str" s="1">
         <v/>
@@ -37524,7 +37524,7 @@
         <v/>
       </c>
       <c r="AC165" t="str" s="2">
-        <v/>
+        <v>Super Aerial</v>
       </c>
       <c r="AD165" t="str" s="2">
         <v/>
@@ -37655,7 +37655,7 @@
         <v/>
       </c>
       <c r="AC166" t="str" s="1">
-        <v/>
+        <v>Real Jerker 508-2</v>
       </c>
       <c r="AD166" t="str" s="1">
         <v/>
@@ -37786,7 +37786,7 @@
         <v/>
       </c>
       <c r="AC167" t="str" s="2">
-        <v/>
+        <v>Real Jerker 508-3</v>
       </c>
       <c r="AD167" t="str" s="2">
         <v/>
@@ -37917,7 +37917,7 @@
         <v/>
       </c>
       <c r="AC168" t="str" s="1">
-        <v/>
+        <v>Real Jerker 508-4</v>
       </c>
       <c r="AD168" t="str" s="1">
         <v/>
@@ -38048,7 +38048,7 @@
         <v/>
       </c>
       <c r="AC169" t="str" s="2">
-        <v/>
+        <v>Slow Jerker 603-1</v>
       </c>
       <c r="AD169" t="str" s="2">
         <v/>
@@ -38179,7 +38179,7 @@
         <v/>
       </c>
       <c r="AC170" t="str" s="1">
-        <v/>
+        <v>Slow Jerker 603-1.5</v>
       </c>
       <c r="AD170" t="str" s="1">
         <v/>
@@ -38310,7 +38310,7 @@
         <v/>
       </c>
       <c r="AC171" t="str" s="2">
-        <v/>
+        <v>Slow Jerker 603-2</v>
       </c>
       <c r="AD171" t="str" s="2">
         <v/>
@@ -38441,7 +38441,7 @@
         <v/>
       </c>
       <c r="AC172" t="str" s="1">
-        <v/>
+        <v>Slow Jerker 603-3</v>
       </c>
       <c r="AD172" t="str" s="1">
         <v/>
@@ -38572,7 +38572,7 @@
         <v/>
       </c>
       <c r="AC173" t="str" s="2">
-        <v/>
+        <v>Slow Jerker 603-4</v>
       </c>
       <c r="AD173" t="str" s="2">
         <v/>
@@ -38703,7 +38703,7 @@
         <v/>
       </c>
       <c r="AC174" t="str" s="1">
-        <v/>
+        <v>Slow Jerker 603-5</v>
       </c>
       <c r="AD174" t="str" s="1">
         <v/>
@@ -38834,7 +38834,7 @@
         <v/>
       </c>
       <c r="AC175" t="str" s="2">
-        <v/>
+        <v>Slow Jerker 603-6</v>
       </c>
       <c r="AD175" t="str" s="2">
         <v/>
@@ -38965,7 +38965,7 @@
         <v/>
       </c>
       <c r="AC176" t="str" s="1">
-        <v/>
+        <v>Long Fall Jerker 77XH</v>
       </c>
       <c r="AD176" t="str" s="1">
         <v/>
@@ -39096,7 +39096,7 @@
         <v/>
       </c>
       <c r="AC177" t="str" s="2">
-        <v/>
+        <v>Long Fall Jerker 710L-1.5</v>
       </c>
       <c r="AD177" t="str" s="2">
         <v/>
@@ -39227,7 +39227,7 @@
         <v/>
       </c>
       <c r="AC178" t="str" s="1">
-        <v/>
+        <v>Long Fall Jerker 710ML-2</v>
       </c>
       <c r="AD178" t="str" s="1">
         <v/>
@@ -39358,7 +39358,7 @@
         <v/>
       </c>
       <c r="AC179" t="str" s="2">
-        <v/>
+        <v>Long Fall Jerker 710M-3</v>
       </c>
       <c r="AD179" t="str" s="2">
         <v/>
@@ -39489,7 +39489,7 @@
         <v/>
       </c>
       <c r="AC180" t="str" s="1">
-        <v/>
+        <v>Long Fall Jerker 710MH-4</v>
       </c>
       <c r="AD180" t="str" s="1">
         <v/>
@@ -39620,7 +39620,7 @@
         <v/>
       </c>
       <c r="AC181" t="str" s="2">
-        <v/>
+        <v>Long Fall Jerker 710H-5</v>
       </c>
       <c r="AD181" t="str" s="2">
         <v/>
@@ -39751,7 +39751,7 @@
         <v/>
       </c>
       <c r="AC182" t="str" s="1">
-        <v/>
+        <v>Long Fall Jerker 710H-6</v>
       </c>
       <c r="AD182" t="str" s="1">
         <v/>
@@ -39882,7 +39882,7 @@
         <v/>
       </c>
       <c r="AC183" t="str" s="2">
-        <v/>
+        <v>High Pitch Jerker 410</v>
       </c>
       <c r="AD183" t="str" s="2">
         <v/>
@@ -40013,7 +40013,7 @@
         <v/>
       </c>
       <c r="AC184" t="str" s="1">
-        <v/>
+        <v>High Pitch Jerker 501</v>
       </c>
       <c r="AD184" t="str" s="1">
         <v/>
@@ -40144,7 +40144,7 @@
         <v/>
       </c>
       <c r="AC185" t="str" s="2">
-        <v/>
+        <v>High Pitch Jerker 504</v>
       </c>
       <c r="AD185" t="str" s="2">
         <v/>
@@ -40275,7 +40275,7 @@
         <v/>
       </c>
       <c r="AC186" t="str" s="1">
-        <v/>
+        <v>High Pitch Jerker 600</v>
       </c>
       <c r="AD186" t="str" s="1">
         <v/>
@@ -40406,7 +40406,7 @@
         <v/>
       </c>
       <c r="AC187" t="str" s="2">
-        <v/>
+        <v>High Pitch Jerker Light 606L-4</v>
       </c>
       <c r="AD187" t="str" s="2">
         <v/>
@@ -40537,7 +40537,7 @@
         <v/>
       </c>
       <c r="AC188" t="str" s="1">
-        <v/>
+        <v>High Pitch Jerker Light 607L-3</v>
       </c>
       <c r="AD188" t="str" s="1">
         <v/>
@@ -40668,7 +40668,7 @@
         <v/>
       </c>
       <c r="AC189" t="str" s="2">
-        <v/>
+        <v>Spin Jerker 500</v>
       </c>
       <c r="AD189" t="str" s="2">
         <v/>
@@ -40799,7 +40799,7 @@
         <v/>
       </c>
       <c r="AC190" t="str" s="1">
-        <v/>
+        <v>Spin Jerker 502</v>
       </c>
       <c r="AD190" t="str" s="1">
         <v/>
@@ -40930,7 +40930,7 @@
         <v/>
       </c>
       <c r="AC191" t="str" s="2">
-        <v/>
+        <v>Spin Jerker 602</v>
       </c>
       <c r="AD191" t="str" s="2">
         <v/>
@@ -41061,7 +41061,7 @@
         <v/>
       </c>
       <c r="AC192" t="str" s="1">
-        <v/>
+        <v>Spin Jerker Light 603L-1.5</v>
       </c>
       <c r="AD192" t="str" s="1">
         <v/>
@@ -41192,7 +41192,7 @@
         <v/>
       </c>
       <c r="AC193" t="str" s="2">
-        <v/>
+        <v>Spin Jerker Light 603L</v>
       </c>
       <c r="AD193" t="str" s="2">
         <v/>
@@ -41323,7 +41323,7 @@
         <v/>
       </c>
       <c r="AC194" t="str" s="1">
-        <v/>
+        <v>Spin Jerker Light 603L-5</v>
       </c>
       <c r="AD194" t="str" s="1">
         <v/>
@@ -41454,7 +41454,7 @@
         <v/>
       </c>
       <c r="AC195" t="str" s="2">
-        <v/>
+        <v>PSMC-66L/MLST</v>
       </c>
       <c r="AD195" t="str" s="2">
         <v/>
@@ -41585,7 +41585,7 @@
         <v/>
       </c>
       <c r="AC196" t="str" s="1">
-        <v/>
+        <v>PSMC-68UL/MLST</v>
       </c>
       <c r="AD196" t="str" s="1">
         <v/>
@@ -41716,7 +41716,7 @@
         <v/>
       </c>
       <c r="AC197" t="str" s="2">
-        <v/>
+        <v>PSMS-70L/M</v>
       </c>
       <c r="AD197" t="str" s="2">
         <v/>
@@ -41847,7 +41847,7 @@
         <v/>
       </c>
       <c r="AC198" t="str" s="1">
-        <v/>
+        <v>PSMS-68UL/MLST</v>
       </c>
       <c r="AD198" t="str" s="1">
         <v/>
@@ -41978,7 +41978,7 @@
         <v/>
       </c>
       <c r="AC199" t="str" s="2">
-        <v/>
+        <v>MS Dancer 61</v>
       </c>
       <c r="AD199" t="str" s="2">
         <v/>
@@ -42109,7 +42109,7 @@
         <v/>
       </c>
       <c r="AC200" t="str" s="1">
-        <v/>
+        <v>Draggin Master C63</v>
       </c>
       <c r="AD200" t="str" s="1">
         <v/>
@@ -42240,7 +42240,7 @@
         <v/>
       </c>
       <c r="AC201" t="str" s="2">
-        <v/>
+        <v>Sword Tip Master C611</v>
       </c>
       <c r="AD201" t="str" s="2">
         <v/>
@@ -42371,7 +42371,7 @@
         <v/>
       </c>
       <c r="AC202" t="str" s="1">
-        <v/>
+        <v>Deep Emotion 70</v>
       </c>
       <c r="AD202" t="str" s="1">
         <v/>
@@ -42502,7 +42502,7 @@
         <v/>
       </c>
       <c r="AC203" t="str" s="2">
-        <v/>
+        <v>Whip Jerk 73</v>
       </c>
       <c r="AD203" t="str" s="2">
         <v/>
@@ -42633,7 +42633,7 @@
         <v/>
       </c>
       <c r="AC204" t="str" s="1">
-        <v/>
+        <v>Lash Jerk 75</v>
       </c>
       <c r="AD204" t="str" s="1">
         <v/>
@@ -42764,7 +42764,7 @@
         <v/>
       </c>
       <c r="AC205" t="str" s="2">
-        <v/>
+        <v>Feather Jerk 77</v>
       </c>
       <c r="AD205" t="str" s="2">
         <v/>
@@ -42895,7 +42895,7 @@
         <v/>
       </c>
       <c r="AC206" t="str" s="1">
-        <v/>
+        <v>Technimaster 82</v>
       </c>
       <c r="AD206" t="str" s="1">
         <v/>
@@ -43026,7 +43026,7 @@
         <v/>
       </c>
       <c r="AC207" t="str" s="2">
-        <v/>
+        <v>Feather Jerk 86</v>
       </c>
       <c r="AD207" t="str" s="2">
         <v/>
@@ -43157,7 +43157,7 @@
         <v/>
       </c>
       <c r="AC208" t="str" s="1">
-        <v/>
+        <v>Slackmaster 86</v>
       </c>
       <c r="AD208" t="str" s="1">
         <v/>
@@ -43288,7 +43288,7 @@
         <v/>
       </c>
       <c r="AC209" t="str" s="2">
-        <v/>
+        <v>Slack Master 86EX</v>
       </c>
       <c r="AD209" t="str" s="2">
         <v/>
@@ -43419,7 +43419,7 @@
         <v/>
       </c>
       <c r="AC210" t="str" s="1">
-        <v/>
+        <v>Razor King 86</v>
       </c>
       <c r="AD210" t="str" s="1">
         <v/>
@@ -43550,7 +43550,7 @@
         <v/>
       </c>
       <c r="AC211" t="str" s="2">
-        <v/>
+        <v>Slackmaster 90</v>
       </c>
       <c r="AD211" t="str" s="2">
         <v/>
@@ -43681,7 +43681,7 @@
         <v/>
       </c>
       <c r="AC212" t="str" s="1">
-        <v/>
+        <v>Slack King 110</v>
       </c>
       <c r="AD212" t="str" s="1">
         <v/>
@@ -43812,7 +43812,7 @@
         <v/>
       </c>
       <c r="AC213" t="str" s="2">
-        <v/>
+        <v>Draggin Master S63</v>
       </c>
       <c r="AD213" t="str" s="2">
         <v/>
@@ -43943,7 +43943,7 @@
         <v/>
       </c>
       <c r="AC214" t="str" s="1">
-        <v/>
+        <v>Sword Tip Master S70</v>
       </c>
       <c r="AD214" t="str" s="1">
         <v/>
@@ -44074,7 +44074,7 @@
         <v/>
       </c>
       <c r="AC215" t="str" s="2">
-        <v/>
+        <v>Response Master 80</v>
       </c>
       <c r="AD215" t="str" s="2">
         <v/>
@@ -44205,7 +44205,7 @@
         <v/>
       </c>
       <c r="AC216" t="str" s="1">
-        <v/>
+        <v>Slack Jerk 88</v>
       </c>
       <c r="AD216" t="str" s="1">
         <v/>
@@ -44336,7 +44336,7 @@
         <v/>
       </c>
       <c r="AC217" t="str" s="2">
-        <v/>
+        <v>Slack Jerk 92</v>
       </c>
       <c r="AD217" t="str" s="2">
         <v/>
@@ -44467,7 +44467,7 @@
         <v/>
       </c>
       <c r="AC218" t="str" s="1">
-        <v/>
+        <v>Razor Jerk 86</v>
       </c>
       <c r="AD218" t="str" s="1">
         <v/>
@@ -44598,7 +44598,7 @@
         <v/>
       </c>
       <c r="AC219" t="str" s="2">
-        <v/>
+        <v>Razor Jerk 90</v>
       </c>
       <c r="AD219" t="str" s="2">
         <v/>
@@ -44729,7 +44729,7 @@
         <v/>
       </c>
       <c r="AC220" t="str" s="1">
-        <v/>
+        <v>Magnum Jerk 710</v>
       </c>
       <c r="AD220" t="str" s="1">
         <v/>
@@ -44860,7 +44860,7 @@
         <v/>
       </c>
       <c r="AC221" t="str" s="2">
-        <v/>
+        <v>Magnum Jerk 84</v>
       </c>
       <c r="AD221" t="str" s="2">
         <v/>
@@ -44991,7 +44991,7 @@
         <v/>
       </c>
       <c r="AC222" t="str" s="1">
-        <v/>
+        <v>Gran Fury</v>
       </c>
       <c r="AD222" t="str" s="1">
         <v/>
@@ -45122,7 +45122,7 @@
         <v/>
       </c>
       <c r="AC223" t="str" s="2">
-        <v/>
+        <v>Gran Sword</v>
       </c>
       <c r="AD223" t="str" s="2">
         <v/>
@@ -45253,7 +45253,7 @@
         <v/>
       </c>
       <c r="AC224" t="str" s="1">
-        <v/>
+        <v>Close Combat 78</v>
       </c>
       <c r="AD224" t="str" s="1">
         <v/>
@@ -45384,7 +45384,7 @@
         <v/>
       </c>
       <c r="AC225" t="str" s="2">
-        <v/>
+        <v>Fast Break 85</v>
       </c>
       <c r="AD225" t="str" s="2">
         <v/>
@@ -45515,7 +45515,7 @@
         <v/>
       </c>
       <c r="AC226" t="str" s="1">
-        <v/>
+        <v>Stream Whip 87</v>
       </c>
       <c r="AD226" t="str" s="1">
         <v/>
@@ -45646,7 +45646,7 @@
         <v/>
       </c>
       <c r="AC227" t="str" s="2">
-        <v/>
+        <v>Mighty Slugger 87</v>
       </c>
       <c r="AD227" t="str" s="2">
         <v/>
@@ -45777,7 +45777,7 @@
         <v/>
       </c>
       <c r="AC228" t="str" s="1">
-        <v/>
+        <v>Sweep Master 91</v>
       </c>
       <c r="AD228" t="str" s="1">
         <v/>
@@ -45908,7 +45908,7 @@
         <v/>
       </c>
       <c r="AC229" t="str" s="2">
-        <v/>
+        <v>Wide Attacker 92</v>
       </c>
       <c r="AD229" t="str" s="2">
         <v/>
@@ -46039,7 +46039,7 @@
         <v/>
       </c>
       <c r="AC230" t="str" s="1">
-        <v/>
+        <v>Pathbreaker 93</v>
       </c>
       <c r="AD230" t="str" s="1">
         <v/>
@@ -46170,7 +46170,7 @@
         <v/>
       </c>
       <c r="AC231" t="str" s="2">
-        <v/>
+        <v>Final Whip 96</v>
       </c>
       <c r="AD231" t="str" s="2">
         <v/>
@@ -46301,7 +46301,7 @@
         <v/>
       </c>
       <c r="AC232" t="str" s="1">
-        <v/>
+        <v>Stream Whip 96</v>
       </c>
       <c r="AD232" t="str" s="1">
         <v/>
@@ -46432,7 +46432,7 @@
         <v/>
       </c>
       <c r="AC233" t="str" s="2">
-        <v/>
+        <v>Stream King 96</v>
       </c>
       <c r="AD233" t="str" s="2">
         <v/>
@@ -46563,7 +46563,7 @@
         <v/>
       </c>
       <c r="AC234" t="str" s="1">
-        <v/>
+        <v>Ace Attacker 96</v>
       </c>
       <c r="AD234" t="str" s="1">
         <v/>
@@ -46694,7 +46694,7 @@
         <v/>
       </c>
       <c r="AC235" t="str" s="2">
-        <v/>
+        <v>Mighty Slugger 98</v>
       </c>
       <c r="AD235" t="str" s="2">
         <v/>
@@ -46825,7 +46825,7 @@
         <v/>
       </c>
       <c r="AC236" t="str" s="1">
-        <v/>
+        <v>Mighty Slugger 98EX</v>
       </c>
       <c r="AD236" t="str" s="1">
         <v/>
@@ -46956,7 +46956,7 @@
         <v/>
       </c>
       <c r="AC237" t="str" s="2">
-        <v/>
+        <v>Supremacy 102AGS</v>
       </c>
       <c r="AD237" t="str" s="2">
         <v/>
@@ -47087,7 +47087,7 @@
         <v/>
       </c>
       <c r="AC238" t="str" s="1">
-        <v/>
+        <v>Harpoon 103</v>
       </c>
       <c r="AD238" t="str" s="1">
         <v/>
@@ -47218,7 +47218,7 @@
         <v/>
       </c>
       <c r="AC239" t="str" s="2">
-        <v/>
+        <v>Shore Patrol 108</v>
       </c>
       <c r="AD239" t="str" s="2">
         <v/>
@@ -47349,7 +47349,7 @@
         <v/>
       </c>
       <c r="AC240" t="str" s="1">
-        <v/>
+        <v>Flex Master 118</v>
       </c>
       <c r="AD240" t="str" s="1">
         <v/>
@@ -47480,7 +47480,7 @@
         <v/>
       </c>
       <c r="AC241" t="str" s="2">
-        <v/>
+        <v>Solid Solution UFT 86</v>
       </c>
       <c r="AD241" t="str" s="2">
         <v/>
@@ -47611,7 +47611,7 @@
         <v/>
       </c>
       <c r="AC242" t="str" s="1">
-        <v/>
+        <v>Solid Solution GRT 88</v>
       </c>
       <c r="AD242" t="str" s="1">
         <v/>
@@ -47742,7 +47742,7 @@
         <v/>
       </c>
       <c r="AC243" t="str" s="2">
-        <v/>
+        <v>Deep Sense C</v>
       </c>
       <c r="AD243" t="str" s="2">
         <v/>
@@ -47873,7 +47873,7 @@
         <v/>
       </c>
       <c r="AC244" t="str" s="1">
-        <v/>
+        <v>Twiggy</v>
       </c>
       <c r="AD244" t="str" s="1">
         <v/>
@@ -48004,7 +48004,7 @@
         <v/>
       </c>
       <c r="AC245" t="str" s="2">
-        <v/>
+        <v>Fine Sensor</v>
       </c>
       <c r="AD245" t="str" s="2">
         <v/>
@@ -48135,7 +48135,7 @@
         <v/>
       </c>
       <c r="AC246" t="str" s="1">
-        <v/>
+        <v>Superior</v>
       </c>
       <c r="AD246" t="str" s="1">
         <v/>
@@ -48266,7 +48266,7 @@
         <v/>
       </c>
       <c r="AC247" t="str" s="2">
-        <v/>
+        <v>Deep Sense S</v>
       </c>
       <c r="AD247" t="str" s="2">
         <v/>
@@ -48397,7 +48397,7 @@
         <v/>
       </c>
       <c r="AC248" t="str" s="1">
-        <v/>
+        <v>Super Twiggy</v>
       </c>
       <c r="AD248" t="str" s="1">
         <v/>
@@ -48528,7 +48528,7 @@
         <v/>
       </c>
       <c r="AC249" t="str" s="2">
-        <v/>
+        <v>Limber Tip SS</v>
       </c>
       <c r="AD249" t="str" s="2">
         <v/>
@@ -48659,7 +48659,7 @@
         <v/>
       </c>
       <c r="AC250" t="str" s="1">
-        <v/>
+        <v>Super D Attacker</v>
       </c>
       <c r="AD250" t="str" s="1">
         <v/>
@@ -48790,7 +48790,7 @@
         <v/>
       </c>
       <c r="AC251" t="str" s="2">
-        <v/>
+        <v>Sharp Cut</v>
       </c>
       <c r="AD251" t="str" s="2">
         <v/>
@@ -48921,7 +48921,7 @@
         <v/>
       </c>
       <c r="AC252" t="str" s="1">
-        <v/>
+        <v>Thunder Shot</v>
       </c>
       <c r="AD252" t="str" s="1">
         <v/>
@@ -49052,7 +49052,7 @@
         <v/>
       </c>
       <c r="AC253" t="str" s="2">
-        <v/>
+        <v>Scout Master</v>
       </c>
       <c r="AD253" t="str" s="2">
         <v/>
@@ -49183,7 +49183,7 @@
         <v/>
       </c>
       <c r="AC254" t="str" s="1">
-        <v/>
+        <v>Reliance</v>
       </c>
       <c r="AD254" t="str" s="1">
         <v/>
@@ -49314,7 +49314,7 @@
         <v/>
       </c>
       <c r="AC255" t="str" s="2">
-        <v/>
+        <v>Mighty Huntsman</v>
       </c>
       <c r="AD255" t="str" s="2">
         <v/>
@@ -49445,7 +49445,7 @@
         <v/>
       </c>
       <c r="AC256" t="str" s="1">
-        <v/>
+        <v>Maneuver</v>
       </c>
       <c r="AD256" t="str" s="1">
         <v/>
@@ -49576,7 +49576,7 @@
         <v/>
       </c>
       <c r="AC257" t="str" s="2">
-        <v/>
+        <v>Prospector</v>
       </c>
       <c r="AD257" t="str" s="2">
         <v/>
@@ -49707,7 +49707,7 @@
         <v/>
       </c>
       <c r="AC258" t="str" s="1">
-        <v/>
+        <v>Multi Potential</v>
       </c>
       <c r="AD258" t="str" s="1">
         <v/>
@@ -49838,7 +49838,7 @@
         <v/>
       </c>
       <c r="AC259" t="str" s="2">
-        <v/>
+        <v>Game Finder</v>
       </c>
       <c r="AD259" t="str" s="2">
         <v/>
@@ -49969,7 +49969,7 @@
         <v/>
       </c>
       <c r="AC260" t="str" s="1">
-        <v/>
+        <v>Petit Pricker</v>
       </c>
       <c r="AD260" t="str" s="1">
         <v/>
@@ -50100,7 +50100,7 @@
         <v/>
       </c>
       <c r="AC261" t="str" s="2">
-        <v/>
+        <v>Super Sensor</v>
       </c>
       <c r="AD261" t="str" s="2">
         <v/>
@@ -50231,7 +50231,7 @@
         <v/>
       </c>
       <c r="AC262" t="str" s="1">
-        <v/>
+        <v>Limber Tip</v>
       </c>
       <c r="AD262" t="str" s="1">
         <v/>
@@ -50362,7 +50362,7 @@
         <v/>
       </c>
       <c r="AC263" t="str" s="2">
-        <v/>
+        <v>D Attacker</v>
       </c>
       <c r="AD263" t="str" s="2">
         <v/>
@@ -50493,7 +50493,7 @@
         <v/>
       </c>
       <c r="AC264" t="str" s="1">
-        <v/>
+        <v>BB Hitman</v>
       </c>
       <c r="AD264" t="str" s="1">
         <v/>
@@ -50624,7 +50624,7 @@
         <v/>
       </c>
       <c r="AC265" t="str" s="2">
-        <v/>
+        <v>Limit Breaker</v>
       </c>
       <c r="AD265" t="str" s="2">
         <v/>
@@ -50755,7 +50755,7 @@
         <v/>
       </c>
       <c r="AC266" t="str" s="1">
-        <v/>
+        <v>Rocky Dagger</v>
       </c>
       <c r="AD266" t="str" s="1">
         <v/>
@@ -50886,7 +50886,7 @@
         <v/>
       </c>
       <c r="AC267" t="str" s="2">
-        <v/>
+        <v>Wide Receiver</v>
       </c>
       <c r="AD267" t="str" s="2">
         <v/>
@@ -51017,7 +51017,7 @@
         <v/>
       </c>
       <c r="AC268" t="str" s="1">
-        <v/>
+        <v>Wild Card</v>
       </c>
       <c r="AD268" t="str" s="1">
         <v/>
@@ -51148,7 +51148,7 @@
         <v/>
       </c>
       <c r="AC269" t="str" s="2">
-        <v/>
+        <v>Light Tough</v>
       </c>
       <c r="AD269" t="str" s="2">
         <v/>
@@ -51279,7 +51279,7 @@
         <v/>
       </c>
       <c r="AC270" t="str" s="1">
-        <v/>
+        <v>Rocky Huntsman</v>
       </c>
       <c r="AD270" t="str" s="1">
         <v/>
@@ -51410,7 +51410,7 @@
         <v/>
       </c>
       <c r="AC271" t="str" s="2">
-        <v/>
+        <v>Marksman</v>
       </c>
       <c r="AD271" t="str" s="2">
         <v/>
@@ -51541,7 +51541,7 @@
         <v/>
       </c>
       <c r="AC272" t="str" s="1">
-        <v/>
+        <v>NEOS-60XUL-S</v>
       </c>
       <c r="AD272" t="str" s="1">
         <v/>
@@ -51672,7 +51672,7 @@
         <v/>
       </c>
       <c r="AC273" t="str" s="2">
-        <v/>
+        <v>NEOS-63SL-S</v>
       </c>
       <c r="AD273" t="str" s="2">
         <v/>
@@ -51803,7 +51803,7 @@
         <v/>
       </c>
       <c r="AC274" t="str" s="1">
-        <v/>
+        <v>NEOS-610UL-S</v>
       </c>
       <c r="AD274" t="str" s="1">
         <v/>
@@ -51934,7 +51934,7 @@
         <v/>
       </c>
       <c r="AC275" t="str" s="2">
-        <v/>
+        <v>NEOS-70L-S</v>
       </c>
       <c r="AD275" t="str" s="2">
         <v/>
@@ -52065,7 +52065,7 @@
         <v/>
       </c>
       <c r="AC276" t="str" s="1">
-        <v/>
+        <v>NEOS-77ML-S</v>
       </c>
       <c r="AD276" t="str" s="1">
         <v/>
@@ -52196,7 +52196,7 @@
         <v/>
       </c>
       <c r="AC277" t="str" s="2">
-        <v/>
+        <v>NEOS-64L+R-T</v>
       </c>
       <c r="AD277" t="str" s="2">
         <v/>
@@ -52327,7 +52327,7 @@
         <v/>
       </c>
       <c r="AC278" t="str" s="1">
-        <v/>
+        <v>NEOS-73M+R-T</v>
       </c>
       <c r="AD278" t="str" s="1">
         <v/>
@@ -52458,7 +52458,7 @@
         <v/>
       </c>
       <c r="AC279" t="str" s="2">
-        <v/>
+        <v>NEOS-76M-T</v>
       </c>
       <c r="AD279" t="str" s="2">
         <v/>
@@ -52589,7 +52589,7 @@
         <v/>
       </c>
       <c r="AC280" t="str" s="1">
-        <v/>
+        <v>NEOS-78MH-T</v>
       </c>
       <c r="AD280" t="str" s="1">
         <v/>
@@ -52720,7 +52720,7 @@
         <v/>
       </c>
       <c r="AC281" t="str" s="2">
-        <v/>
+        <v>NEOS-79MH+R-T</v>
       </c>
       <c r="AD281" t="str" s="2">
         <v/>
@@ -52851,7 +52851,7 @@
         <v/>
       </c>
       <c r="AC282" t="str" s="1">
-        <v/>
+        <v>NEOS-82H-T</v>
       </c>
       <c r="AD282" t="str" s="1">
         <v/>
@@ -52982,7 +52982,7 @@
         <v/>
       </c>
       <c r="AC283" t="str" s="2">
-        <v/>
+        <v>NEOS-84MH-T</v>
       </c>
       <c r="AD283" t="str" s="2">
         <v/>
@@ -53113,7 +53113,7 @@
         <v/>
       </c>
       <c r="AC284" t="str" s="1">
-        <v/>
+        <v>AATS-61UL/R</v>
       </c>
       <c r="AD284" t="str" s="1">
         <v/>
@@ -53244,7 +53244,7 @@
         <v/>
       </c>
       <c r="AC285" t="str" s="2">
-        <v/>
+        <v>AATS-61L/RF</v>
       </c>
       <c r="AD285" t="str" s="2">
         <v/>
@@ -53375,7 +53375,7 @@
         <v/>
       </c>
       <c r="AC286" t="str" s="1">
-        <v/>
+        <v>AATS-61ML/S</v>
       </c>
       <c r="AD286" t="str" s="1">
         <v/>
@@ -53506,7 +53506,7 @@
         <v/>
       </c>
       <c r="AC287" t="str" s="2">
-        <v/>
+        <v>AATS-62MH/R</v>
       </c>
       <c r="AD287" t="str" s="2">
         <v/>
@@ -53637,7 +53637,7 @@
         <v/>
       </c>
       <c r="AC288" t="str" s="1">
-        <v/>
+        <v>AATS-60MLST/F</v>
       </c>
       <c r="AD288" t="str" s="1">
         <v/>
@@ -53768,7 +53768,7 @@
         <v/>
       </c>
       <c r="AC289" t="str" s="2">
-        <v/>
+        <v>AMSC-410</v>
       </c>
       <c r="AD289" t="str" s="2">
         <v/>
@@ -53899,7 +53899,7 @@
         <v/>
       </c>
       <c r="AC290" t="str" s="1">
-        <v/>
+        <v>AMSS-52</v>
       </c>
       <c r="AD290" t="str" s="1">
         <v/>
@@ -54030,7 +54030,7 @@
         <v/>
       </c>
       <c r="AC291" t="str" s="2">
-        <v/>
+        <v>AMSS-510</v>
       </c>
       <c r="AD291" t="str" s="2">
         <v/>
@@ -54161,7 +54161,7 @@
         <v/>
       </c>
       <c r="AC292" t="str" s="1">
-        <v/>
+        <v>Cobra RS Aurora Edition</v>
       </c>
       <c r="AD292" t="str" s="1">
         <v/>
@@ -54292,7 +54292,7 @@
         <v/>
       </c>
       <c r="AC293" t="str" s="2">
-        <v/>
+        <v>Super Stallion RS Aurora Edition</v>
       </c>
       <c r="AD293" t="str" s="2">
         <v/>
